--- a/outputs/synthese_scenarios.xlsx
+++ b/outputs/synthese_scenarios.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>scenario</t>
   </si>
@@ -63,10 +63,7 @@
     <t>relaxation_lp</t>
   </si>
   <si>
-    <t>campaigns</t>
-  </si>
-  <si>
-    <t>campaigns_relaxation_lp</t>
+    <t>campaigns_same_week</t>
   </si>
   <si>
     <t>hrc_plus_10</t>
@@ -448,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -497,19 +494,19 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>33038237.17532879</v>
+        <v>33208877.17532879</v>
       </c>
       <c r="D2">
-        <v>0.937660199822858</v>
+        <v>180.0918675998691</v>
       </c>
       <c r="E2">
-        <v>1020</v>
+        <v>4144</v>
       </c>
       <c r="F2">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -528,9 +525,6 @@
       </c>
       <c r="L2" t="b">
         <v>0</v>
-      </c>
-      <c r="M2">
-        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -538,19 +532,19 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>33327211.93050334</v>
+        <v>33497851.93055335</v>
       </c>
       <c r="D3">
-        <v>0.06066079996526241</v>
+        <v>0.20816809986718</v>
       </c>
       <c r="E3">
-        <v>1020</v>
+        <v>4144</v>
       </c>
       <c r="F3">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="G3">
         <v>49</v>
@@ -576,19 +570,19 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>25535141.32040497</v>
+        <v>25649381.32040497</v>
       </c>
       <c r="D4">
-        <v>12.09974409989081</v>
+        <v>14.64226230001077</v>
       </c>
       <c r="E4">
-        <v>1100</v>
+        <v>1136</v>
       </c>
       <c r="F4">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="G4">
         <v>37</v>
@@ -607,9 +601,6 @@
       </c>
       <c r="L4" t="b">
         <v>0</v>
-      </c>
-      <c r="M4">
-        <v>767</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -617,34 +608,34 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>32651651.12098346</v>
+        <v>24397541.14986853</v>
       </c>
       <c r="D5">
-        <v>0.07083840016275644</v>
+        <v>179.9294046999421</v>
       </c>
       <c r="E5">
-        <v>1100</v>
+        <v>4144</v>
       </c>
       <c r="F5">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5">
-        <v>13720</v>
+        <v>13076</v>
       </c>
       <c r="J5">
         <v>17201</v>
       </c>
       <c r="K5">
-        <v>0.7976280448811116</v>
+        <v>0.7601883611417941</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -655,34 +646,34 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>24226901.14986853</v>
+        <v>33208877.17532879</v>
       </c>
       <c r="D6">
-        <v>1.02293650014326</v>
+        <v>180.0249296999536</v>
       </c>
       <c r="E6">
-        <v>1020</v>
+        <v>4144</v>
       </c>
       <c r="F6">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="G6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6">
-        <v>13076</v>
+        <v>13551</v>
       </c>
       <c r="J6">
         <v>17201</v>
       </c>
       <c r="K6">
-        <v>0.7601883611417941</v>
+        <v>0.7878030347072844</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -693,74 +684,36 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>33038237.17532879</v>
+        <v>33937343.27759257</v>
       </c>
       <c r="D7">
-        <v>0.4949904999230057</v>
+        <v>180.0378501000814</v>
       </c>
       <c r="E7">
-        <v>1020</v>
+        <v>4214</v>
       </c>
       <c r="F7">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="G7">
         <v>50</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>13551</v>
+        <v>13376</v>
       </c>
       <c r="J7">
-        <v>17201</v>
+        <v>17501</v>
       </c>
       <c r="K7">
-        <v>0.7878030347072844</v>
+        <v>0.764299182903834</v>
       </c>
       <c r="L7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>33766703.27759257</v>
-      </c>
-      <c r="D8">
-        <v>0.5690275998786092</v>
-      </c>
-      <c r="E8">
-        <v>1040</v>
-      </c>
-      <c r="F8">
-        <v>189</v>
-      </c>
-      <c r="G8">
-        <v>50</v>
-      </c>
-      <c r="H8">
-        <v>17</v>
-      </c>
-      <c r="I8">
-        <v>13376</v>
-      </c>
-      <c r="J8">
-        <v>17501</v>
-      </c>
-      <c r="K8">
-        <v>0.764299182903834</v>
-      </c>
-      <c r="L8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -771,15 +724,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -799,7 +752,7 @@
         <v>3375</v>
       </c>
       <c r="C2">
-        <v>27617048.55394908</v>
+        <v>27787688.55394908</v>
       </c>
       <c r="D2">
         <v>0.6142084762513808</v>
@@ -810,171 +763,86 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="B3">
-        <v>4050</v>
+        <v>4725</v>
       </c>
       <c r="C3">
-        <v>28977560.52400723</v>
+        <v>30470171.45301107</v>
       </c>
       <c r="D3">
-        <v>0.6496133945700832</v>
+        <v>0.6843206790302889</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="B4">
-        <v>4725</v>
+        <v>6075</v>
       </c>
       <c r="C4">
-        <v>30299531.45301107</v>
+        <v>32888970.91494475</v>
       </c>
       <c r="D4">
-        <v>0.6843206790302889</v>
+        <v>0.755711877216441</v>
       </c>
       <c r="E4">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>5400</v>
+        <v>6750</v>
       </c>
       <c r="C5">
-        <v>31587542.81795882</v>
+        <v>33208877.17532879</v>
       </c>
       <c r="D5">
-        <v>0.7208301842916109</v>
+        <v>0.7878030347072844</v>
       </c>
       <c r="E5">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="B6">
-        <v>6075</v>
+        <v>7425.000000000001</v>
       </c>
       <c r="C6">
-        <v>32718330.91494474</v>
+        <v>33208877.17532879</v>
       </c>
       <c r="D6">
-        <v>0.755711877216441</v>
+        <v>0.7878030347072844</v>
       </c>
       <c r="E6">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="B7">
-        <v>6750</v>
+        <v>10125</v>
       </c>
       <c r="C7">
-        <v>33038237.17532879</v>
+        <v>33208877.17532879</v>
       </c>
       <c r="D7">
         <v>0.7878030347072844</v>
       </c>
       <c r="E7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>1.1</v>
-      </c>
-      <c r="B8">
-        <v>7425.000000000001</v>
-      </c>
-      <c r="C8">
-        <v>33038237.17532879</v>
-      </c>
-      <c r="D8">
-        <v>0.7878030347072844</v>
-      </c>
-      <c r="E8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>1.2</v>
-      </c>
-      <c r="B9">
-        <v>8100</v>
-      </c>
-      <c r="C9">
-        <v>33038237.17532879</v>
-      </c>
-      <c r="D9">
-        <v>0.7878030347072844</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>1.3</v>
-      </c>
-      <c r="B10">
-        <v>8775</v>
-      </c>
-      <c r="C10">
-        <v>33038237.17532879</v>
-      </c>
-      <c r="D10">
-        <v>0.7878030347072844</v>
-      </c>
-      <c r="E10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>1.4</v>
-      </c>
-      <c r="B11">
-        <v>9450</v>
-      </c>
-      <c r="C11">
-        <v>33038237.17532879</v>
-      </c>
-      <c r="D11">
-        <v>0.7878030347072844</v>
-      </c>
-      <c r="E11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>1.5</v>
-      </c>
-      <c r="B12">
-        <v>10125</v>
-      </c>
-      <c r="C12">
-        <v>33038237.17532879</v>
-      </c>
-      <c r="D12">
-        <v>0.7878030347072844</v>
-      </c>
-      <c r="E12">
         <v>50</v>
       </c>
     </row>
@@ -990,7 +858,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -1002,7 +870,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1010,7 +878,7 @@
         <v>0.95</v>
       </c>
       <c r="B2">
-        <v>32924737.17532879</v>
+        <v>33095377.17532879</v>
       </c>
       <c r="C2">
         <v>0.7878030347072844</v>
@@ -1019,7 +887,7 @@
         <v>50</v>
       </c>
       <c r="E2">
-        <v>0.9778604506630603</v>
+        <v>0.8650630179326292</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1027,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>33038237.17532879</v>
+        <v>33208877.17532879</v>
       </c>
       <c r="C3">
         <v>0.7878030347072844</v>
@@ -1036,7 +904,7 @@
         <v>50</v>
       </c>
       <c r="E3">
-        <v>0.9664902998236333</v>
+        <v>0.9664902998236332</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1044,7 +912,7 @@
         <v>1.05</v>
       </c>
       <c r="B4">
-        <v>33038237.17532879</v>
+        <v>33208877.17532879</v>
       </c>
       <c r="C4">
         <v>0.7878030347072844</v>
@@ -1053,7 +921,7 @@
         <v>50</v>
       </c>
       <c r="E4">
-        <v>0.9204669522129841</v>
+        <v>0.920466952212984</v>
       </c>
     </row>
   </sheetData>
